--- a/DATA BARANG YAMAHA.xlsx
+++ b/DATA BARANG YAMAHA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\PUBLIC SHARING\3_DATABASE ---------------------\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0696ba9f31ccbbf1/ドキュメント/Belajar/scanner/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{BFD40037-D786-40AC-9B45-03D6D5B780C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E162A88A-C4C9-4FAC-85DF-B8FF0CDA47C9}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{E162A88A-C4C9-4FAC-85DF-B8FF0CDA47C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -714,15 +712,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{693E8667-D994-485F-AF97-D75500216F98}">
   <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -739,7 +737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -756,7 +754,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
@@ -773,7 +771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>3</v>
       </c>
@@ -790,7 +788,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
@@ -807,7 +805,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -824,7 +822,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>6</v>
       </c>
@@ -841,7 +839,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>7</v>
       </c>
@@ -858,7 +856,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>8</v>
       </c>
@@ -875,7 +873,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>9</v>
       </c>
@@ -892,7 +890,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>10</v>
       </c>
@@ -909,7 +907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>11</v>
       </c>
@@ -926,7 +924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>12</v>
       </c>
@@ -943,7 +941,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>13</v>
       </c>
@@ -960,7 +958,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>14</v>
       </c>
@@ -977,7 +975,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>15</v>
       </c>
@@ -994,7 +992,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>16</v>
       </c>
@@ -1011,7 +1009,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -1028,7 +1026,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>18</v>
       </c>
@@ -1045,7 +1043,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>19</v>
       </c>
@@ -1062,7 +1060,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>20</v>
       </c>
@@ -1079,7 +1077,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>21</v>
       </c>
@@ -1096,7 +1094,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>22</v>
       </c>
@@ -1113,7 +1111,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>23</v>
       </c>
@@ -1130,7 +1128,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="10">
         <v>24</v>
       </c>
@@ -1147,7 +1145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>25</v>
       </c>
@@ -1164,7 +1162,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10">
         <v>26</v>
       </c>
@@ -1181,7 +1179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>27</v>
       </c>
@@ -1198,7 +1196,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="10">
         <v>28</v>
       </c>
@@ -1215,7 +1213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>29</v>
       </c>
@@ -1232,7 +1230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="10">
         <v>30</v>
       </c>
@@ -1249,7 +1247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>31</v>
       </c>
@@ -1266,7 +1264,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="10">
         <v>32</v>
       </c>
@@ -1283,7 +1281,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>33</v>
       </c>
@@ -1300,7 +1298,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="10">
         <v>34</v>
       </c>
@@ -1317,7 +1315,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>35</v>
       </c>
@@ -1334,7 +1332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="10">
         <v>36</v>
       </c>
@@ -1351,7 +1349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>37</v>
       </c>
@@ -1368,7 +1366,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="10">
         <v>38</v>
       </c>
@@ -1385,7 +1383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>39</v>
       </c>
@@ -1402,7 +1400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="10">
         <v>40</v>
       </c>
@@ -1419,7 +1417,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>41</v>
       </c>
@@ -1436,7 +1434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="10">
         <v>42</v>
       </c>
@@ -1453,7 +1451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>43</v>
       </c>
@@ -1470,7 +1468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="10">
         <v>44</v>
       </c>
@@ -1487,7 +1485,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>45</v>
       </c>
@@ -1504,7 +1502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="10">
         <v>46</v>
       </c>
@@ -1521,7 +1519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>47</v>
       </c>
@@ -1538,7 +1536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="10">
         <v>48</v>
       </c>
@@ -1555,7 +1553,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>49</v>
       </c>
@@ -1572,7 +1570,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="10">
         <v>50</v>
       </c>
@@ -1589,7 +1587,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>51</v>
       </c>
@@ -1604,7 +1602,7 @@
       </c>
       <c r="E52" s="14"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="10">
         <v>52</v>
       </c>
@@ -1621,7 +1619,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="10"/>
       <c r="B54" s="17" t="s">
         <v>67</v>
